--- a/data/花店价格/花趣饿了么/花趣饿了么价格.xlsx
+++ b/data/花店价格/花趣饿了么/花趣饿了么价格.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C447"/>
+  <dimension ref="A1:G447"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,12 +436,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>xixi</t>
+          <t>自定义ID</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
           <t>价格</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>活动总库存</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>每日活动库存</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>每人/活动期间限购</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>每人/每日限购</t>
         </is>
       </c>
     </row>
@@ -457,6 +477,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -470,6 +498,14 @@
           <t>128.0</t>
         </is>
       </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -483,6 +519,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -496,6 +540,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -509,6 +561,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -522,6 +582,14 @@
           <t>198.0</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -535,6 +603,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -548,6 +624,14 @@
           <t>188.0</t>
         </is>
       </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -561,6 +645,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -574,6 +666,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -587,6 +687,14 @@
           <t>188.0</t>
         </is>
       </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -600,6 +708,14 @@
           <t>138.0</t>
         </is>
       </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -613,6 +729,14 @@
           <t>188.0</t>
         </is>
       </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -626,6 +750,14 @@
           <t>368.0</t>
         </is>
       </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -639,6 +771,14 @@
           <t>388.0</t>
         </is>
       </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -652,6 +792,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -665,6 +813,14 @@
           <t>298.0</t>
         </is>
       </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -678,6 +834,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -691,6 +855,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -704,6 +876,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -717,6 +897,14 @@
           <t>138.0</t>
         </is>
       </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -730,6 +918,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -743,6 +939,14 @@
           <t>138.0</t>
         </is>
       </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -756,6 +960,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -769,6 +981,14 @@
           <t>488.0</t>
         </is>
       </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -782,6 +1002,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -795,6 +1023,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -808,6 +1044,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -821,6 +1065,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -834,6 +1086,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -847,6 +1107,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -860,6 +1128,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -873,6 +1149,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -886,6 +1170,14 @@
           <t>138.0</t>
         </is>
       </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -899,6 +1191,14 @@
           <t>108.0</t>
         </is>
       </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -912,6 +1212,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -925,6 +1233,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -938,6 +1254,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -951,6 +1275,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -964,6 +1296,14 @@
           <t>138.0</t>
         </is>
       </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -977,6 +1317,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -990,6 +1338,14 @@
           <t>158.0</t>
         </is>
       </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr"/>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1003,6 +1359,14 @@
           <t>188.0</t>
         </is>
       </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr"/>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1016,6 +1380,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr"/>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1029,6 +1401,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1042,6 +1422,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr"/>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1055,6 +1443,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1068,6 +1464,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr"/>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1081,6 +1485,14 @@
           <t>208.0</t>
         </is>
       </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr"/>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1094,6 +1506,14 @@
           <t>488.0</t>
         </is>
       </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr"/>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1107,6 +1527,14 @@
           <t>148.0</t>
         </is>
       </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1120,6 +1548,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr"/>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1133,6 +1569,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr"/>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1146,6 +1590,14 @@
           <t>228.0</t>
         </is>
       </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr"/>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1159,6 +1611,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1172,6 +1632,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr"/>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1185,6 +1653,14 @@
           <t>159.0</t>
         </is>
       </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1198,6 +1674,14 @@
           <t>149.0</t>
         </is>
       </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1211,6 +1695,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr"/>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -1224,6 +1716,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr"/>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -1237,6 +1737,14 @@
           <t>78.0</t>
         </is>
       </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr"/>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -1250,6 +1758,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D63" t="inlineStr"/>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="inlineStr"/>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -1263,6 +1779,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D64" t="inlineStr"/>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="inlineStr"/>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -1276,6 +1800,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D65" t="inlineStr"/>
+      <c r="E65" t="inlineStr"/>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -1289,6 +1821,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" t="inlineStr"/>
+      <c r="F66" t="inlineStr"/>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -1302,6 +1842,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D67" t="inlineStr"/>
+      <c r="E67" t="inlineStr"/>
+      <c r="F67" t="inlineStr"/>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -1315,6 +1863,14 @@
           <t>1888.0</t>
         </is>
       </c>
+      <c r="D68" t="inlineStr"/>
+      <c r="E68" t="inlineStr"/>
+      <c r="F68" t="inlineStr"/>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -1328,6 +1884,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D69" t="inlineStr"/>
+      <c r="E69" t="inlineStr"/>
+      <c r="F69" t="inlineStr"/>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -1341,6 +1905,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D70" t="inlineStr"/>
+      <c r="E70" t="inlineStr"/>
+      <c r="F70" t="inlineStr"/>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -1354,6 +1926,14 @@
           <t>88.0</t>
         </is>
       </c>
+      <c r="D71" t="inlineStr"/>
+      <c r="E71" t="inlineStr"/>
+      <c r="F71" t="inlineStr"/>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -1367,6 +1947,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" t="inlineStr"/>
+      <c r="F72" t="inlineStr"/>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -1380,6 +1968,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" t="inlineStr"/>
+      <c r="F73" t="inlineStr"/>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -1393,6 +1989,14 @@
           <t>139.0</t>
         </is>
       </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" t="inlineStr"/>
+      <c r="F74" t="inlineStr"/>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -1406,6 +2010,14 @@
           <t>139.0</t>
         </is>
       </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr"/>
+      <c r="F75" t="inlineStr"/>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -1419,6 +2031,14 @@
           <t>149.0</t>
         </is>
       </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" t="inlineStr"/>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -1432,6 +2052,14 @@
           <t>328.0</t>
         </is>
       </c>
+      <c r="D77" t="inlineStr"/>
+      <c r="E77" t="inlineStr"/>
+      <c r="F77" t="inlineStr"/>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -1445,6 +2073,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" t="inlineStr"/>
+      <c r="F78" t="inlineStr"/>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -1458,6 +2094,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" t="inlineStr"/>
+      <c r="F79" t="inlineStr"/>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -1471,6 +2115,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D80" t="inlineStr"/>
+      <c r="E80" t="inlineStr"/>
+      <c r="F80" t="inlineStr"/>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -1484,6 +2136,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="inlineStr"/>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -1497,6 +2157,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" t="inlineStr"/>
+      <c r="F82" t="inlineStr"/>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -1510,6 +2178,14 @@
           <t>138.0</t>
         </is>
       </c>
+      <c r="D83" t="inlineStr"/>
+      <c r="E83" t="inlineStr"/>
+      <c r="F83" t="inlineStr"/>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -1523,6 +2199,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D84" t="inlineStr"/>
+      <c r="E84" t="inlineStr"/>
+      <c r="F84" t="inlineStr"/>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -1536,6 +2220,14 @@
           <t>188.0</t>
         </is>
       </c>
+      <c r="D85" t="inlineStr"/>
+      <c r="E85" t="inlineStr"/>
+      <c r="F85" t="inlineStr"/>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -1549,6 +2241,14 @@
           <t>149.0</t>
         </is>
       </c>
+      <c r="D86" t="inlineStr"/>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="inlineStr"/>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -1562,6 +2262,14 @@
           <t>149.0</t>
         </is>
       </c>
+      <c r="D87" t="inlineStr"/>
+      <c r="E87" t="inlineStr"/>
+      <c r="F87" t="inlineStr"/>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -1575,6 +2283,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D88" t="inlineStr"/>
+      <c r="E88" t="inlineStr"/>
+      <c r="F88" t="inlineStr"/>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -1588,6 +2304,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D89" t="inlineStr"/>
+      <c r="E89" t="inlineStr"/>
+      <c r="F89" t="inlineStr"/>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -1601,6 +2325,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D90" t="inlineStr"/>
+      <c r="E90" t="inlineStr"/>
+      <c r="F90" t="inlineStr"/>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -1614,6 +2346,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D91" t="inlineStr"/>
+      <c r="E91" t="inlineStr"/>
+      <c r="F91" t="inlineStr"/>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -1627,6 +2367,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D92" t="inlineStr"/>
+      <c r="E92" t="inlineStr"/>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -1640,6 +2388,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D93" t="inlineStr"/>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -1653,6 +2409,14 @@
           <t>188.0</t>
         </is>
       </c>
+      <c r="D94" t="inlineStr"/>
+      <c r="E94" t="inlineStr"/>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -1666,6 +2430,14 @@
           <t>488.0</t>
         </is>
       </c>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -1679,6 +2451,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D96" t="inlineStr"/>
+      <c r="E96" t="inlineStr"/>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -1692,6 +2472,14 @@
           <t>148.0</t>
         </is>
       </c>
+      <c r="D97" t="inlineStr"/>
+      <c r="E97" t="inlineStr"/>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -1705,6 +2493,14 @@
           <t>148.0</t>
         </is>
       </c>
+      <c r="D98" t="inlineStr"/>
+      <c r="E98" t="inlineStr"/>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -1718,6 +2514,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D99" t="inlineStr"/>
+      <c r="E99" t="inlineStr"/>
+      <c r="F99" t="inlineStr"/>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -1731,6 +2535,14 @@
           <t>388.0</t>
         </is>
       </c>
+      <c r="D100" t="inlineStr"/>
+      <c r="E100" t="inlineStr"/>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -1744,6 +2556,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -1757,6 +2577,14 @@
           <t>118.0</t>
         </is>
       </c>
+      <c r="D102" t="inlineStr"/>
+      <c r="E102" t="inlineStr"/>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -1770,6 +2598,14 @@
           <t>288.0</t>
         </is>
       </c>
+      <c r="D103" t="inlineStr"/>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -1783,6 +2619,14 @@
           <t>78.0</t>
         </is>
       </c>
+      <c r="D104" t="inlineStr"/>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -1796,6 +2640,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D105" t="inlineStr"/>
+      <c r="E105" t="inlineStr"/>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -1809,6 +2661,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D106" t="inlineStr"/>
+      <c r="E106" t="inlineStr"/>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -1822,6 +2682,14 @@
           <t>198.0</t>
         </is>
       </c>
+      <c r="D107" t="inlineStr"/>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -1835,6 +2703,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -1848,6 +2724,14 @@
           <t>128.0</t>
         </is>
       </c>
+      <c r="D109" t="inlineStr"/>
+      <c r="E109" t="inlineStr"/>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -1861,6 +2745,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D110" t="inlineStr"/>
+      <c r="E110" t="inlineStr"/>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -1874,6 +2766,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D111" t="inlineStr"/>
+      <c r="E111" t="inlineStr"/>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -1887,6 +2787,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -1900,6 +2808,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D113" t="inlineStr"/>
+      <c r="E113" t="inlineStr"/>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -1913,6 +2829,14 @@
           <t>78.0</t>
         </is>
       </c>
+      <c r="D114" t="inlineStr"/>
+      <c r="E114" t="inlineStr"/>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -1926,6 +2850,14 @@
           <t>88.0</t>
         </is>
       </c>
+      <c r="D115" t="inlineStr"/>
+      <c r="E115" t="inlineStr"/>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -1939,6 +2871,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D116" t="inlineStr"/>
+      <c r="E116" t="inlineStr"/>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -1952,6 +2892,14 @@
           <t>118.0</t>
         </is>
       </c>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -1965,6 +2913,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D118" t="inlineStr"/>
+      <c r="E118" t="inlineStr"/>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -1978,6 +2934,14 @@
           <t>328.0</t>
         </is>
       </c>
+      <c r="D119" t="inlineStr"/>
+      <c r="E119" t="inlineStr"/>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -1991,6 +2955,14 @@
           <t>138.0</t>
         </is>
       </c>
+      <c r="D120" t="inlineStr"/>
+      <c r="E120" t="inlineStr"/>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -2004,6 +2976,14 @@
           <t>128.0</t>
         </is>
       </c>
+      <c r="D121" t="inlineStr"/>
+      <c r="E121" t="inlineStr"/>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -2017,6 +2997,14 @@
           <t>149.0</t>
         </is>
       </c>
+      <c r="D122" t="inlineStr"/>
+      <c r="E122" t="inlineStr"/>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -2030,6 +3018,14 @@
           <t>138.0</t>
         </is>
       </c>
+      <c r="D123" t="inlineStr"/>
+      <c r="E123" t="inlineStr"/>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -2043,6 +3039,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D124" t="inlineStr"/>
+      <c r="E124" t="inlineStr"/>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -2056,6 +3060,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D125" t="inlineStr"/>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -2069,6 +3081,14 @@
           <t>118.0</t>
         </is>
       </c>
+      <c r="D126" t="inlineStr"/>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -2082,6 +3102,14 @@
           <t>78.0</t>
         </is>
       </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -2095,6 +3123,14 @@
           <t>118.0</t>
         </is>
       </c>
+      <c r="D128" t="inlineStr"/>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -2108,6 +3144,14 @@
           <t>128.0</t>
         </is>
       </c>
+      <c r="D129" t="inlineStr"/>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -2121,6 +3165,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D130" t="inlineStr"/>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -2134,6 +3186,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D131" t="inlineStr"/>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -2147,6 +3207,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D132" t="inlineStr"/>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -2160,6 +3228,14 @@
           <t>208.0</t>
         </is>
       </c>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -2173,6 +3249,14 @@
           <t>139.0</t>
         </is>
       </c>
+      <c r="D134" t="inlineStr"/>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -2186,6 +3270,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D135" t="inlineStr"/>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -2199,6 +3291,14 @@
           <t>238.0</t>
         </is>
       </c>
+      <c r="D136" t="inlineStr"/>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -2212,6 +3312,14 @@
           <t>188.0</t>
         </is>
       </c>
+      <c r="D137" t="inlineStr"/>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -2225,6 +3333,14 @@
           <t>268.0</t>
         </is>
       </c>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -2238,6 +3354,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D139" t="inlineStr"/>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -2251,6 +3375,14 @@
           <t>188.0</t>
         </is>
       </c>
+      <c r="D140" t="inlineStr"/>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -2264,6 +3396,14 @@
           <t>238.0</t>
         </is>
       </c>
+      <c r="D141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -2277,6 +3417,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -2290,6 +3438,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D143" t="inlineStr"/>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -2303,6 +3459,14 @@
           <t>158.0</t>
         </is>
       </c>
+      <c r="D144" t="inlineStr"/>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -2316,6 +3480,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D145" t="inlineStr"/>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -2329,6 +3501,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D146" t="inlineStr"/>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -2342,6 +3522,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -2355,6 +3543,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D148" t="inlineStr"/>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -2368,6 +3564,14 @@
           <t>488.0</t>
         </is>
       </c>
+      <c r="D149" t="inlineStr"/>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -2381,6 +3585,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D150" t="inlineStr"/>
+      <c r="E150" t="inlineStr"/>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -2394,6 +3606,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -2407,6 +3627,14 @@
           <t>148.0</t>
         </is>
       </c>
+      <c r="D152" t="inlineStr"/>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -2420,6 +3648,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D153" t="inlineStr"/>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -2433,6 +3669,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D154" t="inlineStr"/>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -2446,6 +3690,14 @@
           <t>4998.0</t>
         </is>
       </c>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -2459,6 +3711,14 @@
           <t>288.0</t>
         </is>
       </c>
+      <c r="D156" t="inlineStr"/>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -2472,6 +3732,14 @@
           <t>158.0</t>
         </is>
       </c>
+      <c r="D157" t="inlineStr"/>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -2485,6 +3753,14 @@
           <t>208.0</t>
         </is>
       </c>
+      <c r="D158" t="inlineStr"/>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -2498,6 +3774,14 @@
           <t>298.0</t>
         </is>
       </c>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -2511,6 +3795,14 @@
           <t>138.0</t>
         </is>
       </c>
+      <c r="D160" t="inlineStr"/>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -2524,6 +3816,14 @@
           <t>268.0</t>
         </is>
       </c>
+      <c r="D161" t="inlineStr"/>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -2537,6 +3837,14 @@
           <t>488.0</t>
         </is>
       </c>
+      <c r="D162" t="inlineStr"/>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -2550,6 +3858,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -2563,6 +3879,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D164" t="inlineStr"/>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -2576,6 +3900,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D165" t="inlineStr"/>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -2589,6 +3921,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D166" t="inlineStr"/>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -2602,6 +3942,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D167" t="inlineStr"/>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -2615,6 +3963,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D168" t="inlineStr"/>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -2628,6 +3984,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D169" t="inlineStr"/>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -2641,6 +4005,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D170" t="inlineStr"/>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -2654,6 +4026,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D171" t="inlineStr"/>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -2667,6 +4047,14 @@
           <t>328.0</t>
         </is>
       </c>
+      <c r="D172" t="inlineStr"/>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -2680,6 +4068,14 @@
           <t>258.0</t>
         </is>
       </c>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -2693,6 +4089,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D174" t="inlineStr"/>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -2706,6 +4110,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D175" t="inlineStr"/>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -2719,6 +4131,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -2732,6 +4152,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D177" t="inlineStr"/>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -2745,6 +4173,14 @@
           <t>298.0</t>
         </is>
       </c>
+      <c r="D178" t="inlineStr"/>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -2758,6 +4194,14 @@
           <t>158.0</t>
         </is>
       </c>
+      <c r="D179" t="inlineStr"/>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -2771,6 +4215,14 @@
           <t>268.0</t>
         </is>
       </c>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -2784,6 +4236,14 @@
           <t>78.0</t>
         </is>
       </c>
+      <c r="D181" t="inlineStr"/>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -2797,6 +4257,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D182" t="inlineStr"/>
+      <c r="E182" t="inlineStr"/>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -2810,6 +4278,14 @@
           <t>328.0</t>
         </is>
       </c>
+      <c r="D183" t="inlineStr"/>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -2823,6 +4299,14 @@
           <t>188.0</t>
         </is>
       </c>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -2836,6 +4320,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D185" t="inlineStr"/>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -2849,6 +4341,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D186" t="inlineStr"/>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -2862,6 +4362,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -2875,6 +4383,14 @@
           <t>148.0</t>
         </is>
       </c>
+      <c r="D188" t="inlineStr"/>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -2888,6 +4404,14 @@
           <t>268.0</t>
         </is>
       </c>
+      <c r="D189" t="inlineStr"/>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -2901,6 +4425,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D190" t="inlineStr"/>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -2914,6 +4446,14 @@
           <t>388.0</t>
         </is>
       </c>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -2927,6 +4467,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D192" t="inlineStr"/>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -2940,6 +4488,14 @@
           <t>158.0</t>
         </is>
       </c>
+      <c r="D193" t="inlineStr"/>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -2953,6 +4509,14 @@
           <t>158.0</t>
         </is>
       </c>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -2966,6 +4530,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D195" t="inlineStr"/>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -2979,6 +4551,14 @@
           <t>158.0</t>
         </is>
       </c>
+      <c r="D196" t="inlineStr"/>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -2992,6 +4572,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D197" t="inlineStr"/>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -3005,6 +4593,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D198" t="inlineStr"/>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -3018,6 +4614,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D199" t="inlineStr"/>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -3031,6 +4635,14 @@
           <t>288.0</t>
         </is>
       </c>
+      <c r="D200" t="inlineStr"/>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -3044,6 +4656,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D201" t="inlineStr"/>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -3057,6 +4677,14 @@
           <t>208.0</t>
         </is>
       </c>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -3070,6 +4698,14 @@
           <t>148.0</t>
         </is>
       </c>
+      <c r="D203" t="inlineStr"/>
+      <c r="E203" t="inlineStr"/>
+      <c r="F203" t="inlineStr"/>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -3083,6 +4719,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D204" t="inlineStr"/>
+      <c r="E204" t="inlineStr"/>
+      <c r="F204" t="inlineStr"/>
+      <c r="G204" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -3096,6 +4740,14 @@
           <t>138.0</t>
         </is>
       </c>
+      <c r="D205" t="inlineStr"/>
+      <c r="E205" t="inlineStr"/>
+      <c r="F205" t="inlineStr"/>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -3109,6 +4761,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D206" t="inlineStr"/>
+      <c r="E206" t="inlineStr"/>
+      <c r="F206" t="inlineStr"/>
+      <c r="G206" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -3122,6 +4782,14 @@
           <t>139.0</t>
         </is>
       </c>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -3135,6 +4803,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D208" t="inlineStr"/>
+      <c r="E208" t="inlineStr"/>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -3148,6 +4824,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -3161,6 +4845,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D210" t="inlineStr"/>
+      <c r="E210" t="inlineStr"/>
+      <c r="F210" t="inlineStr"/>
+      <c r="G210" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -3174,6 +4866,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
@@ -3187,6 +4887,14 @@
           <t>288.0</t>
         </is>
       </c>
+      <c r="D212" t="inlineStr"/>
+      <c r="E212" t="inlineStr"/>
+      <c r="F212" t="inlineStr"/>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -3200,6 +4908,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D213" t="inlineStr"/>
+      <c r="E213" t="inlineStr"/>
+      <c r="F213" t="inlineStr"/>
+      <c r="G213" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
@@ -3213,6 +4929,14 @@
           <t>208.0</t>
         </is>
       </c>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -3226,6 +4950,14 @@
           <t>328.0</t>
         </is>
       </c>
+      <c r="D215" t="inlineStr"/>
+      <c r="E215" t="inlineStr"/>
+      <c r="F215" t="inlineStr"/>
+      <c r="G215" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -3239,6 +4971,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D216" t="inlineStr"/>
+      <c r="E216" t="inlineStr"/>
+      <c r="F216" t="inlineStr"/>
+      <c r="G216" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
@@ -3252,6 +4992,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D217" t="inlineStr"/>
+      <c r="E217" t="inlineStr"/>
+      <c r="F217" t="inlineStr"/>
+      <c r="G217" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -3265,6 +5013,14 @@
           <t>238.0</t>
         </is>
       </c>
+      <c r="D218" t="inlineStr"/>
+      <c r="E218" t="inlineStr"/>
+      <c r="F218" t="inlineStr"/>
+      <c r="G218" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
@@ -3278,6 +5034,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D219" t="inlineStr"/>
+      <c r="E219" t="inlineStr"/>
+      <c r="F219" t="inlineStr"/>
+      <c r="G219" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -3291,6 +5055,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D220" t="inlineStr"/>
+      <c r="E220" t="inlineStr"/>
+      <c r="F220" t="inlineStr"/>
+      <c r="G220" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
@@ -3304,6 +5076,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D221" t="inlineStr"/>
+      <c r="E221" t="inlineStr"/>
+      <c r="F221" t="inlineStr"/>
+      <c r="G221" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -3317,6 +5097,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D222" t="inlineStr"/>
+      <c r="E222" t="inlineStr"/>
+      <c r="F222" t="inlineStr"/>
+      <c r="G222" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
@@ -3330,6 +5118,14 @@
           <t>149.0</t>
         </is>
       </c>
+      <c r="D223" t="inlineStr"/>
+      <c r="E223" t="inlineStr"/>
+      <c r="F223" t="inlineStr"/>
+      <c r="G223" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -3343,6 +5139,14 @@
           <t>188.0</t>
         </is>
       </c>
+      <c r="D224" t="inlineStr"/>
+      <c r="E224" t="inlineStr"/>
+      <c r="F224" t="inlineStr"/>
+      <c r="G224" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
@@ -3356,6 +5160,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D225" t="inlineStr"/>
+      <c r="E225" t="inlineStr"/>
+      <c r="F225" t="inlineStr"/>
+      <c r="G225" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
@@ -3369,6 +5181,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -3382,6 +5202,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D227" t="inlineStr"/>
+      <c r="E227" t="inlineStr"/>
+      <c r="F227" t="inlineStr"/>
+      <c r="G227" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
@@ -3395,6 +5223,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
@@ -3408,6 +5244,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D229" t="inlineStr"/>
+      <c r="E229" t="inlineStr"/>
+      <c r="F229" t="inlineStr"/>
+      <c r="G229" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -3421,6 +5265,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -3434,6 +5286,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D231" t="inlineStr"/>
+      <c r="E231" t="inlineStr"/>
+      <c r="F231" t="inlineStr"/>
+      <c r="G231" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -3447,6 +5307,14 @@
           <t>118.0</t>
         </is>
       </c>
+      <c r="D232" t="inlineStr"/>
+      <c r="E232" t="inlineStr"/>
+      <c r="F232" t="inlineStr"/>
+      <c r="G232" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -3460,6 +5328,14 @@
           <t>288.0</t>
         </is>
       </c>
+      <c r="D233" t="inlineStr"/>
+      <c r="E233" t="inlineStr"/>
+      <c r="F233" t="inlineStr"/>
+      <c r="G233" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="234">
       <c r="A234" t="inlineStr">
@@ -3473,6 +5349,14 @@
           <t>198.0</t>
         </is>
       </c>
+      <c r="D234" t="inlineStr"/>
+      <c r="E234" t="inlineStr"/>
+      <c r="F234" t="inlineStr"/>
+      <c r="G234" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="235">
       <c r="A235" t="inlineStr">
@@ -3486,6 +5370,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D235" t="inlineStr"/>
+      <c r="E235" t="inlineStr"/>
+      <c r="F235" t="inlineStr"/>
+      <c r="G235" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -3499,6 +5391,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D236" t="inlineStr"/>
+      <c r="E236" t="inlineStr"/>
+      <c r="F236" t="inlineStr"/>
+      <c r="G236" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="237">
       <c r="A237" t="inlineStr">
@@ -3512,6 +5412,14 @@
           <t>57.0</t>
         </is>
       </c>
+      <c r="D237" t="inlineStr"/>
+      <c r="E237" t="inlineStr"/>
+      <c r="F237" t="inlineStr"/>
+      <c r="G237" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="238">
       <c r="A238" t="inlineStr">
@@ -3525,6 +5433,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D238" t="inlineStr"/>
+      <c r="E238" t="inlineStr"/>
+      <c r="F238" t="inlineStr"/>
+      <c r="G238" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="239">
       <c r="A239" t="inlineStr">
@@ -3538,6 +5454,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D239" t="inlineStr"/>
+      <c r="E239" t="inlineStr"/>
+      <c r="F239" t="inlineStr"/>
+      <c r="G239" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="240">
       <c r="A240" t="inlineStr">
@@ -3551,6 +5475,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D240" t="inlineStr"/>
+      <c r="E240" t="inlineStr"/>
+      <c r="F240" t="inlineStr"/>
+      <c r="G240" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -3564,6 +5496,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="242">
       <c r="A242" t="inlineStr">
@@ -3577,6 +5517,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D242" t="inlineStr"/>
+      <c r="E242" t="inlineStr"/>
+      <c r="F242" t="inlineStr"/>
+      <c r="G242" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -3590,6 +5538,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D243" t="inlineStr"/>
+      <c r="E243" t="inlineStr"/>
+      <c r="F243" t="inlineStr"/>
+      <c r="G243" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -3603,6 +5559,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D244" t="inlineStr"/>
+      <c r="E244" t="inlineStr"/>
+      <c r="F244" t="inlineStr"/>
+      <c r="G244" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="245">
       <c r="A245" t="inlineStr">
@@ -3616,6 +5580,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D245" t="inlineStr"/>
+      <c r="E245" t="inlineStr"/>
+      <c r="F245" t="inlineStr"/>
+      <c r="G245" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="246">
       <c r="A246" t="inlineStr">
@@ -3629,6 +5601,14 @@
           <t>57.0</t>
         </is>
       </c>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="247">
       <c r="A247" t="inlineStr">
@@ -3642,6 +5622,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D247" t="inlineStr"/>
+      <c r="E247" t="inlineStr"/>
+      <c r="F247" t="inlineStr"/>
+      <c r="G247" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="248">
       <c r="A248" t="inlineStr">
@@ -3655,6 +5643,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="249">
       <c r="A249" t="inlineStr">
@@ -3668,6 +5664,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D249" t="inlineStr"/>
+      <c r="E249" t="inlineStr"/>
+      <c r="F249" t="inlineStr"/>
+      <c r="G249" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -3681,6 +5685,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D250" t="inlineStr"/>
+      <c r="E250" t="inlineStr"/>
+      <c r="F250" t="inlineStr"/>
+      <c r="G250" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="251">
       <c r="A251" t="inlineStr">
@@ -3694,6 +5706,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D251" t="inlineStr"/>
+      <c r="E251" t="inlineStr"/>
+      <c r="F251" t="inlineStr"/>
+      <c r="G251" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="252">
       <c r="A252" t="inlineStr">
@@ -3707,6 +5727,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="253">
       <c r="A253" t="inlineStr">
@@ -3720,6 +5748,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D253" t="inlineStr"/>
+      <c r="E253" t="inlineStr"/>
+      <c r="F253" t="inlineStr"/>
+      <c r="G253" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="254">
       <c r="A254" t="inlineStr">
@@ -3733,6 +5769,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="255">
       <c r="A255" t="inlineStr">
@@ -3746,6 +5790,14 @@
           <t>57.0</t>
         </is>
       </c>
+      <c r="D255" t="inlineStr"/>
+      <c r="E255" t="inlineStr"/>
+      <c r="F255" t="inlineStr"/>
+      <c r="G255" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -3759,6 +5811,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D256" t="inlineStr"/>
+      <c r="E256" t="inlineStr"/>
+      <c r="F256" t="inlineStr"/>
+      <c r="G256" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -3772,6 +5832,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D257" t="inlineStr"/>
+      <c r="E257" t="inlineStr"/>
+      <c r="F257" t="inlineStr"/>
+      <c r="G257" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="258">
       <c r="A258" t="inlineStr">
@@ -3785,6 +5853,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D258" t="inlineStr"/>
+      <c r="E258" t="inlineStr"/>
+      <c r="F258" t="inlineStr"/>
+      <c r="G258" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -3798,6 +5874,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D259" t="inlineStr"/>
+      <c r="E259" t="inlineStr"/>
+      <c r="F259" t="inlineStr"/>
+      <c r="G259" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -3811,6 +5895,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D260" t="inlineStr"/>
+      <c r="E260" t="inlineStr"/>
+      <c r="F260" t="inlineStr"/>
+      <c r="G260" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -3824,6 +5916,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D261" t="inlineStr"/>
+      <c r="E261" t="inlineStr"/>
+      <c r="F261" t="inlineStr"/>
+      <c r="G261" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -3837,6 +5937,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D262" t="inlineStr"/>
+      <c r="E262" t="inlineStr"/>
+      <c r="F262" t="inlineStr"/>
+      <c r="G262" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -3850,6 +5958,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D263" t="inlineStr"/>
+      <c r="E263" t="inlineStr"/>
+      <c r="F263" t="inlineStr"/>
+      <c r="G263" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -3863,6 +5979,14 @@
           <t>57.0</t>
         </is>
       </c>
+      <c r="D264" t="inlineStr"/>
+      <c r="E264" t="inlineStr"/>
+      <c r="F264" t="inlineStr"/>
+      <c r="G264" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="265">
       <c r="A265" t="inlineStr">
@@ -3876,6 +6000,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D265" t="inlineStr"/>
+      <c r="E265" t="inlineStr"/>
+      <c r="F265" t="inlineStr"/>
+      <c r="G265" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="266">
       <c r="A266" t="inlineStr">
@@ -3889,6 +6021,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D266" t="inlineStr"/>
+      <c r="E266" t="inlineStr"/>
+      <c r="F266" t="inlineStr"/>
+      <c r="G266" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="267">
       <c r="A267" t="inlineStr">
@@ -3902,6 +6042,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D267" t="inlineStr"/>
+      <c r="E267" t="inlineStr"/>
+      <c r="F267" t="inlineStr"/>
+      <c r="G267" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" t="inlineStr">
@@ -3915,6 +6063,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D268" t="inlineStr"/>
+      <c r="E268" t="inlineStr"/>
+      <c r="F268" t="inlineStr"/>
+      <c r="G268" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -3928,6 +6084,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D269" t="inlineStr"/>
+      <c r="E269" t="inlineStr"/>
+      <c r="F269" t="inlineStr"/>
+      <c r="G269" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="270">
       <c r="A270" t="inlineStr">
@@ -3941,6 +6105,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D270" t="inlineStr"/>
+      <c r="E270" t="inlineStr"/>
+      <c r="F270" t="inlineStr"/>
+      <c r="G270" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="271">
       <c r="A271" t="inlineStr">
@@ -3954,6 +6126,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D271" t="inlineStr"/>
+      <c r="E271" t="inlineStr"/>
+      <c r="F271" t="inlineStr"/>
+      <c r="G271" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -3967,6 +6147,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D272" t="inlineStr"/>
+      <c r="E272" t="inlineStr"/>
+      <c r="F272" t="inlineStr"/>
+      <c r="G272" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -3980,6 +6168,14 @@
           <t>57.0</t>
         </is>
       </c>
+      <c r="D273" t="inlineStr"/>
+      <c r="E273" t="inlineStr"/>
+      <c r="F273" t="inlineStr"/>
+      <c r="G273" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -3993,6 +6189,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D274" t="inlineStr"/>
+      <c r="E274" t="inlineStr"/>
+      <c r="F274" t="inlineStr"/>
+      <c r="G274" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -4006,6 +6210,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D275" t="inlineStr"/>
+      <c r="E275" t="inlineStr"/>
+      <c r="F275" t="inlineStr"/>
+      <c r="G275" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="276">
       <c r="A276" t="inlineStr">
@@ -4019,6 +6231,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D276" t="inlineStr"/>
+      <c r="E276" t="inlineStr"/>
+      <c r="F276" t="inlineStr"/>
+      <c r="G276" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="277">
       <c r="A277" t="inlineStr">
@@ -4032,6 +6252,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D277" t="inlineStr"/>
+      <c r="E277" t="inlineStr"/>
+      <c r="F277" t="inlineStr"/>
+      <c r="G277" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="278">
       <c r="A278" t="inlineStr">
@@ -4045,6 +6273,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D278" t="inlineStr"/>
+      <c r="E278" t="inlineStr"/>
+      <c r="F278" t="inlineStr"/>
+      <c r="G278" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -4058,6 +6294,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D279" t="inlineStr"/>
+      <c r="E279" t="inlineStr"/>
+      <c r="F279" t="inlineStr"/>
+      <c r="G279" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="280">
       <c r="A280" t="inlineStr">
@@ -4071,6 +6315,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D280" t="inlineStr"/>
+      <c r="E280" t="inlineStr"/>
+      <c r="F280" t="inlineStr"/>
+      <c r="G280" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -4084,6 +6336,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D281" t="inlineStr"/>
+      <c r="E281" t="inlineStr"/>
+      <c r="F281" t="inlineStr"/>
+      <c r="G281" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="282">
       <c r="A282" t="inlineStr">
@@ -4097,6 +6357,14 @@
           <t>57.0</t>
         </is>
       </c>
+      <c r="D282" t="inlineStr"/>
+      <c r="E282" t="inlineStr"/>
+      <c r="F282" t="inlineStr"/>
+      <c r="G282" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="283">
       <c r="A283" t="inlineStr">
@@ -4110,6 +6378,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D283" t="inlineStr"/>
+      <c r="E283" t="inlineStr"/>
+      <c r="F283" t="inlineStr"/>
+      <c r="G283" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="284">
       <c r="A284" t="inlineStr">
@@ -4123,6 +6399,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D284" t="inlineStr"/>
+      <c r="E284" t="inlineStr"/>
+      <c r="F284" t="inlineStr"/>
+      <c r="G284" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="285">
       <c r="A285" t="inlineStr">
@@ -4136,6 +6420,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D285" t="inlineStr"/>
+      <c r="E285" t="inlineStr"/>
+      <c r="F285" t="inlineStr"/>
+      <c r="G285" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -4149,6 +6441,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D286" t="inlineStr"/>
+      <c r="E286" t="inlineStr"/>
+      <c r="F286" t="inlineStr"/>
+      <c r="G286" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="287">
       <c r="A287" t="inlineStr">
@@ -4162,6 +6462,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D287" t="inlineStr"/>
+      <c r="E287" t="inlineStr"/>
+      <c r="F287" t="inlineStr"/>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -4175,6 +6483,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D288" t="inlineStr"/>
+      <c r="E288" t="inlineStr"/>
+      <c r="F288" t="inlineStr"/>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -4188,6 +6504,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D289" t="inlineStr"/>
+      <c r="E289" t="inlineStr"/>
+      <c r="F289" t="inlineStr"/>
+      <c r="G289" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="290">
       <c r="A290" t="inlineStr">
@@ -4201,6 +6525,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D290" t="inlineStr"/>
+      <c r="E290" t="inlineStr"/>
+      <c r="F290" t="inlineStr"/>
+      <c r="G290" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -4214,6 +6546,14 @@
           <t>57.0</t>
         </is>
       </c>
+      <c r="D291" t="inlineStr"/>
+      <c r="E291" t="inlineStr"/>
+      <c r="F291" t="inlineStr"/>
+      <c r="G291" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="292">
       <c r="A292" t="inlineStr">
@@ -4227,6 +6567,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D292" t="inlineStr"/>
+      <c r="E292" t="inlineStr"/>
+      <c r="F292" t="inlineStr"/>
+      <c r="G292" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -4240,6 +6588,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D293" t="inlineStr"/>
+      <c r="E293" t="inlineStr"/>
+      <c r="F293" t="inlineStr"/>
+      <c r="G293" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -4253,6 +6609,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D294" t="inlineStr"/>
+      <c r="E294" t="inlineStr"/>
+      <c r="F294" t="inlineStr"/>
+      <c r="G294" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -4266,6 +6630,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D295" t="inlineStr"/>
+      <c r="E295" t="inlineStr"/>
+      <c r="F295" t="inlineStr"/>
+      <c r="G295" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="296">
       <c r="A296" t="inlineStr">
@@ -4279,6 +6651,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D296" t="inlineStr"/>
+      <c r="E296" t="inlineStr"/>
+      <c r="F296" t="inlineStr"/>
+      <c r="G296" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="297">
       <c r="A297" t="inlineStr">
@@ -4292,6 +6672,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D297" t="inlineStr"/>
+      <c r="E297" t="inlineStr"/>
+      <c r="F297" t="inlineStr"/>
+      <c r="G297" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -4305,6 +6693,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D298" t="inlineStr"/>
+      <c r="E298" t="inlineStr"/>
+      <c r="F298" t="inlineStr"/>
+      <c r="G298" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
@@ -4318,6 +6714,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D299" t="inlineStr"/>
+      <c r="E299" t="inlineStr"/>
+      <c r="F299" t="inlineStr"/>
+      <c r="G299" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
@@ -4331,6 +6735,14 @@
           <t>57.0</t>
         </is>
       </c>
+      <c r="D300" t="inlineStr"/>
+      <c r="E300" t="inlineStr"/>
+      <c r="F300" t="inlineStr"/>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -4344,6 +6756,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D301" t="inlineStr"/>
+      <c r="E301" t="inlineStr"/>
+      <c r="F301" t="inlineStr"/>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="302">
       <c r="A302" t="inlineStr">
@@ -4357,6 +6777,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D302" t="inlineStr"/>
+      <c r="E302" t="inlineStr"/>
+      <c r="F302" t="inlineStr"/>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" t="inlineStr">
@@ -4370,6 +6798,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D303" t="inlineStr"/>
+      <c r="E303" t="inlineStr"/>
+      <c r="F303" t="inlineStr"/>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" t="inlineStr">
@@ -4383,6 +6819,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" t="inlineStr"/>
+      <c r="F304" t="inlineStr"/>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="305">
       <c r="A305" t="inlineStr">
@@ -4396,6 +6840,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr"/>
+      <c r="F305" t="inlineStr"/>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="306">
       <c r="A306" t="inlineStr">
@@ -4409,6 +6861,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr"/>
+      <c r="F306" t="inlineStr"/>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -4422,6 +6882,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" t="inlineStr"/>
+      <c r="F307" t="inlineStr"/>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="308">
       <c r="A308" t="inlineStr">
@@ -4435,6 +6903,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" t="inlineStr"/>
+      <c r="F308" t="inlineStr"/>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="309">
       <c r="A309" t="inlineStr">
@@ -4448,6 +6924,14 @@
           <t>57.0</t>
         </is>
       </c>
+      <c r="D309" t="inlineStr"/>
+      <c r="E309" t="inlineStr"/>
+      <c r="F309" t="inlineStr"/>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="310">
       <c r="A310" t="inlineStr">
@@ -4461,6 +6945,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D310" t="inlineStr"/>
+      <c r="E310" t="inlineStr"/>
+      <c r="F310" t="inlineStr"/>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -4474,6 +6966,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" t="inlineStr"/>
+      <c r="F311" t="inlineStr"/>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="312">
       <c r="A312" t="inlineStr">
@@ -4487,6 +6987,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" t="inlineStr"/>
+      <c r="F312" t="inlineStr"/>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="313">
       <c r="A313" t="inlineStr">
@@ -4500,6 +7008,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" t="inlineStr"/>
+      <c r="F313" t="inlineStr"/>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="314">
       <c r="A314" t="inlineStr">
@@ -4513,6 +7029,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" t="inlineStr"/>
+      <c r="F314" t="inlineStr"/>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="315">
       <c r="A315" t="inlineStr">
@@ -4526,6 +7050,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" t="inlineStr"/>
+      <c r="F315" t="inlineStr"/>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="316">
       <c r="A316" t="inlineStr">
@@ -4539,6 +7071,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" t="inlineStr"/>
+      <c r="F316" t="inlineStr"/>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="317">
       <c r="A317" t="inlineStr">
@@ -4552,6 +7092,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr"/>
+      <c r="F317" t="inlineStr"/>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="318">
       <c r="A318" t="inlineStr">
@@ -4565,6 +7113,14 @@
           <t>149.0</t>
         </is>
       </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" t="inlineStr"/>
+      <c r="F318" t="inlineStr"/>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="319">
       <c r="A319" t="inlineStr">
@@ -4578,6 +7134,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" t="inlineStr"/>
+      <c r="F319" t="inlineStr"/>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="320">
       <c r="A320" t="inlineStr">
@@ -4591,6 +7155,14 @@
           <t>148.0</t>
         </is>
       </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" t="inlineStr"/>
+      <c r="F320" t="inlineStr"/>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="321">
       <c r="A321" t="inlineStr">
@@ -4604,6 +7176,14 @@
           <t>288.0</t>
         </is>
       </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" t="inlineStr"/>
+      <c r="F321" t="inlineStr"/>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="322">
       <c r="A322" t="inlineStr">
@@ -4617,6 +7197,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" t="inlineStr"/>
+      <c r="F322" t="inlineStr"/>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="323">
       <c r="A323" t="inlineStr">
@@ -4630,6 +7218,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" t="inlineStr"/>
+      <c r="F323" t="inlineStr"/>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="324">
       <c r="A324" t="inlineStr">
@@ -4643,6 +7239,14 @@
           <t>39.0</t>
         </is>
       </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" t="inlineStr"/>
+      <c r="F324" t="inlineStr"/>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="325">
       <c r="A325" t="inlineStr">
@@ -4656,6 +7260,14 @@
           <t>39.0</t>
         </is>
       </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" t="inlineStr"/>
+      <c r="F325" t="inlineStr"/>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="326">
       <c r="A326" t="inlineStr">
@@ -4669,6 +7281,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D326" t="inlineStr"/>
+      <c r="E326" t="inlineStr"/>
+      <c r="F326" t="inlineStr"/>
+      <c r="G326" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="327">
       <c r="A327" t="inlineStr">
@@ -4682,6 +7302,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D327" t="inlineStr"/>
+      <c r="E327" t="inlineStr"/>
+      <c r="F327" t="inlineStr"/>
+      <c r="G327" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="328">
       <c r="A328" t="inlineStr">
@@ -4695,6 +7323,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D328" t="inlineStr"/>
+      <c r="E328" t="inlineStr"/>
+      <c r="F328" t="inlineStr"/>
+      <c r="G328" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="329">
       <c r="A329" t="inlineStr">
@@ -4708,6 +7344,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D329" t="inlineStr"/>
+      <c r="E329" t="inlineStr"/>
+      <c r="F329" t="inlineStr"/>
+      <c r="G329" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="330">
       <c r="A330" t="inlineStr">
@@ -4721,6 +7365,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D330" t="inlineStr"/>
+      <c r="E330" t="inlineStr"/>
+      <c r="F330" t="inlineStr"/>
+      <c r="G330" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="331">
       <c r="A331" t="inlineStr">
@@ -4734,6 +7386,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D331" t="inlineStr"/>
+      <c r="E331" t="inlineStr"/>
+      <c r="F331" t="inlineStr"/>
+      <c r="G331" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="332">
       <c r="A332" t="inlineStr">
@@ -4747,6 +7407,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D332" t="inlineStr"/>
+      <c r="E332" t="inlineStr"/>
+      <c r="F332" t="inlineStr"/>
+      <c r="G332" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="333">
       <c r="A333" t="inlineStr">
@@ -4760,6 +7428,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D333" t="inlineStr"/>
+      <c r="E333" t="inlineStr"/>
+      <c r="F333" t="inlineStr"/>
+      <c r="G333" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="334">
       <c r="A334" t="inlineStr">
@@ -4773,6 +7449,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D334" t="inlineStr"/>
+      <c r="E334" t="inlineStr"/>
+      <c r="F334" t="inlineStr"/>
+      <c r="G334" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="335">
       <c r="A335" t="inlineStr">
@@ -4786,6 +7470,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D335" t="inlineStr"/>
+      <c r="E335" t="inlineStr"/>
+      <c r="F335" t="inlineStr"/>
+      <c r="G335" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="336">
       <c r="A336" t="inlineStr">
@@ -4799,6 +7491,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D336" t="inlineStr"/>
+      <c r="E336" t="inlineStr"/>
+      <c r="F336" t="inlineStr"/>
+      <c r="G336" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="337">
       <c r="A337" t="inlineStr">
@@ -4812,6 +7512,14 @@
           <t>238.0</t>
         </is>
       </c>
+      <c r="D337" t="inlineStr"/>
+      <c r="E337" t="inlineStr"/>
+      <c r="F337" t="inlineStr"/>
+      <c r="G337" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="338">
       <c r="A338" t="inlineStr">
@@ -4825,6 +7533,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D338" t="inlineStr"/>
+      <c r="E338" t="inlineStr"/>
+      <c r="F338" t="inlineStr"/>
+      <c r="G338" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="339">
       <c r="A339" t="inlineStr">
@@ -4838,6 +7554,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D339" t="inlineStr"/>
+      <c r="E339" t="inlineStr"/>
+      <c r="F339" t="inlineStr"/>
+      <c r="G339" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="340">
       <c r="A340" t="inlineStr">
@@ -4851,6 +7575,14 @@
           <t>238.0</t>
         </is>
       </c>
+      <c r="D340" t="inlineStr"/>
+      <c r="E340" t="inlineStr"/>
+      <c r="F340" t="inlineStr"/>
+      <c r="G340" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="341">
       <c r="A341" t="inlineStr">
@@ -4864,6 +7596,14 @@
           <t>188.0</t>
         </is>
       </c>
+      <c r="D341" t="inlineStr"/>
+      <c r="E341" t="inlineStr"/>
+      <c r="F341" t="inlineStr"/>
+      <c r="G341" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="342">
       <c r="A342" t="inlineStr">
@@ -4877,6 +7617,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D342" t="inlineStr"/>
+      <c r="E342" t="inlineStr"/>
+      <c r="F342" t="inlineStr"/>
+      <c r="G342" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="343">
       <c r="A343" t="inlineStr">
@@ -4890,6 +7638,14 @@
           <t>208.0</t>
         </is>
       </c>
+      <c r="D343" t="inlineStr"/>
+      <c r="E343" t="inlineStr"/>
+      <c r="F343" t="inlineStr"/>
+      <c r="G343" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
@@ -4903,6 +7659,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D344" t="inlineStr"/>
+      <c r="E344" t="inlineStr"/>
+      <c r="F344" t="inlineStr"/>
+      <c r="G344" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="345">
       <c r="A345" t="inlineStr">
@@ -4916,6 +7680,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D345" t="inlineStr"/>
+      <c r="E345" t="inlineStr"/>
+      <c r="F345" t="inlineStr"/>
+      <c r="G345" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="346">
       <c r="A346" t="inlineStr">
@@ -4929,6 +7701,14 @@
           <t>39.0</t>
         </is>
       </c>
+      <c r="D346" t="inlineStr"/>
+      <c r="E346" t="inlineStr"/>
+      <c r="F346" t="inlineStr"/>
+      <c r="G346" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="347">
       <c r="A347" t="inlineStr">
@@ -4942,6 +7722,14 @@
           <t>248.0</t>
         </is>
       </c>
+      <c r="D347" t="inlineStr"/>
+      <c r="E347" t="inlineStr"/>
+      <c r="F347" t="inlineStr"/>
+      <c r="G347" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
@@ -4955,6 +7743,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D348" t="inlineStr"/>
+      <c r="E348" t="inlineStr"/>
+      <c r="F348" t="inlineStr"/>
+      <c r="G348" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="349">
       <c r="A349" t="inlineStr">
@@ -4968,6 +7764,14 @@
           <t>139.0</t>
         </is>
       </c>
+      <c r="D349" t="inlineStr"/>
+      <c r="E349" t="inlineStr"/>
+      <c r="F349" t="inlineStr"/>
+      <c r="G349" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="350">
       <c r="A350" t="inlineStr">
@@ -4981,6 +7785,14 @@
           <t>128.0</t>
         </is>
       </c>
+      <c r="D350" t="inlineStr"/>
+      <c r="E350" t="inlineStr"/>
+      <c r="F350" t="inlineStr"/>
+      <c r="G350" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="351">
       <c r="A351" t="inlineStr">
@@ -4994,6 +7806,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D351" t="inlineStr"/>
+      <c r="E351" t="inlineStr"/>
+      <c r="F351" t="inlineStr"/>
+      <c r="G351" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="352">
       <c r="A352" t="inlineStr">
@@ -5007,6 +7827,14 @@
           <t>39.0</t>
         </is>
       </c>
+      <c r="D352" t="inlineStr"/>
+      <c r="E352" t="inlineStr"/>
+      <c r="F352" t="inlineStr"/>
+      <c r="G352" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="353">
       <c r="A353" t="inlineStr">
@@ -5020,6 +7848,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D353" t="inlineStr"/>
+      <c r="E353" t="inlineStr"/>
+      <c r="F353" t="inlineStr"/>
+      <c r="G353" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="354">
       <c r="A354" t="inlineStr">
@@ -5033,6 +7869,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D354" t="inlineStr"/>
+      <c r="E354" t="inlineStr"/>
+      <c r="F354" t="inlineStr"/>
+      <c r="G354" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="355">
       <c r="A355" t="inlineStr">
@@ -5046,6 +7890,14 @@
           <t>139.0</t>
         </is>
       </c>
+      <c r="D355" t="inlineStr"/>
+      <c r="E355" t="inlineStr"/>
+      <c r="F355" t="inlineStr"/>
+      <c r="G355" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
@@ -5059,6 +7911,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D356" t="inlineStr"/>
+      <c r="E356" t="inlineStr"/>
+      <c r="F356" t="inlineStr"/>
+      <c r="G356" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -5072,6 +7932,14 @@
           <t>248.0</t>
         </is>
       </c>
+      <c r="D357" t="inlineStr"/>
+      <c r="E357" t="inlineStr"/>
+      <c r="F357" t="inlineStr"/>
+      <c r="G357" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="358">
       <c r="A358" t="inlineStr">
@@ -5085,6 +7953,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D358" t="inlineStr"/>
+      <c r="E358" t="inlineStr"/>
+      <c r="F358" t="inlineStr"/>
+      <c r="G358" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="359">
       <c r="A359" t="inlineStr">
@@ -5098,6 +7974,14 @@
           <t>128.0</t>
         </is>
       </c>
+      <c r="D359" t="inlineStr"/>
+      <c r="E359" t="inlineStr"/>
+      <c r="F359" t="inlineStr"/>
+      <c r="G359" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="360">
       <c r="A360" t="inlineStr">
@@ -5111,6 +7995,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D360" t="inlineStr"/>
+      <c r="E360" t="inlineStr"/>
+      <c r="F360" t="inlineStr"/>
+      <c r="G360" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="361">
       <c r="A361" t="inlineStr">
@@ -5124,6 +8016,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D361" t="inlineStr"/>
+      <c r="E361" t="inlineStr"/>
+      <c r="F361" t="inlineStr"/>
+      <c r="G361" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -5137,6 +8037,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D362" t="inlineStr"/>
+      <c r="E362" t="inlineStr"/>
+      <c r="F362" t="inlineStr"/>
+      <c r="G362" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -5150,6 +8058,14 @@
           <t>139.0</t>
         </is>
       </c>
+      <c r="D363" t="inlineStr"/>
+      <c r="E363" t="inlineStr"/>
+      <c r="F363" t="inlineStr"/>
+      <c r="G363" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="364">
       <c r="A364" t="inlineStr">
@@ -5163,6 +8079,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D364" t="inlineStr"/>
+      <c r="E364" t="inlineStr"/>
+      <c r="F364" t="inlineStr"/>
+      <c r="G364" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
@@ -5176,6 +8100,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D365" t="inlineStr"/>
+      <c r="E365" t="inlineStr"/>
+      <c r="F365" t="inlineStr"/>
+      <c r="G365" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="366">
       <c r="A366" t="inlineStr">
@@ -5189,6 +8121,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D366" t="inlineStr"/>
+      <c r="E366" t="inlineStr"/>
+      <c r="F366" t="inlineStr"/>
+      <c r="G366" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -5202,6 +8142,14 @@
           <t>188.0</t>
         </is>
       </c>
+      <c r="D367" t="inlineStr"/>
+      <c r="E367" t="inlineStr"/>
+      <c r="F367" t="inlineStr"/>
+      <c r="G367" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="368">
       <c r="A368" t="inlineStr">
@@ -5215,6 +8163,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D368" t="inlineStr"/>
+      <c r="E368" t="inlineStr"/>
+      <c r="F368" t="inlineStr"/>
+      <c r="G368" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -5228,6 +8184,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D369" t="inlineStr"/>
+      <c r="E369" t="inlineStr"/>
+      <c r="F369" t="inlineStr"/>
+      <c r="G369" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="370">
       <c r="A370" t="inlineStr">
@@ -5241,6 +8205,14 @@
           <t>328.0</t>
         </is>
       </c>
+      <c r="D370" t="inlineStr"/>
+      <c r="E370" t="inlineStr"/>
+      <c r="F370" t="inlineStr"/>
+      <c r="G370" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="371">
       <c r="A371" t="inlineStr">
@@ -5254,6 +8226,14 @@
           <t>158.0</t>
         </is>
       </c>
+      <c r="D371" t="inlineStr"/>
+      <c r="E371" t="inlineStr"/>
+      <c r="F371" t="inlineStr"/>
+      <c r="G371" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="372">
       <c r="A372" t="inlineStr">
@@ -5267,6 +8247,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D372" t="inlineStr"/>
+      <c r="E372" t="inlineStr"/>
+      <c r="F372" t="inlineStr"/>
+      <c r="G372" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="373">
       <c r="A373" t="inlineStr">
@@ -5280,6 +8268,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D373" t="inlineStr"/>
+      <c r="E373" t="inlineStr"/>
+      <c r="F373" t="inlineStr"/>
+      <c r="G373" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="374">
       <c r="A374" t="inlineStr">
@@ -5293,6 +8289,14 @@
           <t>988.0</t>
         </is>
       </c>
+      <c r="D374" t="inlineStr"/>
+      <c r="E374" t="inlineStr"/>
+      <c r="F374" t="inlineStr"/>
+      <c r="G374" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="375">
       <c r="A375" t="inlineStr">
@@ -5306,6 +8310,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D375" t="inlineStr"/>
+      <c r="E375" t="inlineStr"/>
+      <c r="F375" t="inlineStr"/>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="376">
       <c r="A376" t="inlineStr">
@@ -5319,6 +8331,14 @@
           <t>158.0</t>
         </is>
       </c>
+      <c r="D376" t="inlineStr"/>
+      <c r="E376" t="inlineStr"/>
+      <c r="F376" t="inlineStr"/>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="377">
       <c r="A377" t="inlineStr">
@@ -5332,6 +8352,14 @@
           <t>288.0</t>
         </is>
       </c>
+      <c r="D377" t="inlineStr"/>
+      <c r="E377" t="inlineStr"/>
+      <c r="F377" t="inlineStr"/>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="378">
       <c r="A378" t="inlineStr">
@@ -5345,6 +8373,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D378" t="inlineStr"/>
+      <c r="E378" t="inlineStr"/>
+      <c r="F378" t="inlineStr"/>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
@@ -5358,6 +8394,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D379" t="inlineStr"/>
+      <c r="E379" t="inlineStr"/>
+      <c r="F379" t="inlineStr"/>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="380">
       <c r="A380" t="inlineStr">
@@ -5371,6 +8415,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D380" t="inlineStr"/>
+      <c r="E380" t="inlineStr"/>
+      <c r="F380" t="inlineStr"/>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="381">
       <c r="A381" t="inlineStr">
@@ -5384,6 +8436,14 @@
           <t>29.9</t>
         </is>
       </c>
+      <c r="D381" t="inlineStr"/>
+      <c r="E381" t="inlineStr"/>
+      <c r="F381" t="inlineStr"/>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="382">
       <c r="A382" t="inlineStr">
@@ -5397,6 +8457,14 @@
           <t>29.9</t>
         </is>
       </c>
+      <c r="D382" t="inlineStr"/>
+      <c r="E382" t="inlineStr"/>
+      <c r="F382" t="inlineStr"/>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -5410,6 +8478,14 @@
           <t>29.9</t>
         </is>
       </c>
+      <c r="D383" t="inlineStr"/>
+      <c r="E383" t="inlineStr"/>
+      <c r="F383" t="inlineStr"/>
+      <c r="G383" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="384">
       <c r="A384" t="inlineStr">
@@ -5423,6 +8499,14 @@
           <t>29.9</t>
         </is>
       </c>
+      <c r="D384" t="inlineStr"/>
+      <c r="E384" t="inlineStr"/>
+      <c r="F384" t="inlineStr"/>
+      <c r="G384" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="385">
       <c r="A385" t="inlineStr">
@@ -5436,6 +8520,14 @@
           <t>29.9</t>
         </is>
       </c>
+      <c r="D385" t="inlineStr"/>
+      <c r="E385" t="inlineStr"/>
+      <c r="F385" t="inlineStr"/>
+      <c r="G385" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="386">
       <c r="A386" t="inlineStr">
@@ -5449,6 +8541,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D386" t="inlineStr"/>
+      <c r="E386" t="inlineStr"/>
+      <c r="F386" t="inlineStr"/>
+      <c r="G386" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -5462,6 +8562,14 @@
           <t>504.0</t>
         </is>
       </c>
+      <c r="D387" t="inlineStr"/>
+      <c r="E387" t="inlineStr"/>
+      <c r="F387" t="inlineStr"/>
+      <c r="G387" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="388">
       <c r="A388" t="inlineStr">
@@ -5475,6 +8583,14 @@
           <t>358.0</t>
         </is>
       </c>
+      <c r="D388" t="inlineStr"/>
+      <c r="E388" t="inlineStr"/>
+      <c r="F388" t="inlineStr"/>
+      <c r="G388" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="389">
       <c r="A389" t="inlineStr">
@@ -5488,6 +8604,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D389" t="inlineStr"/>
+      <c r="E389" t="inlineStr"/>
+      <c r="F389" t="inlineStr"/>
+      <c r="G389" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="390">
       <c r="A390" t="inlineStr">
@@ -5501,6 +8625,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D390" t="inlineStr"/>
+      <c r="E390" t="inlineStr"/>
+      <c r="F390" t="inlineStr"/>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="391">
       <c r="A391" t="inlineStr">
@@ -5514,6 +8646,14 @@
           <t>138.0</t>
         </is>
       </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr"/>
+      <c r="F391" t="inlineStr"/>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="392">
       <c r="A392" t="inlineStr">
@@ -5527,6 +8667,14 @@
           <t>158.0</t>
         </is>
       </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" t="inlineStr"/>
+      <c r="F392" t="inlineStr"/>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="393">
       <c r="A393" t="inlineStr">
@@ -5540,6 +8688,14 @@
           <t>448.0</t>
         </is>
       </c>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="inlineStr"/>
+      <c r="F393" t="inlineStr"/>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="394">
       <c r="A394" t="inlineStr">
@@ -5553,6 +8709,14 @@
           <t>328.0</t>
         </is>
       </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" t="inlineStr"/>
+      <c r="F394" t="inlineStr"/>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="395">
       <c r="A395" t="inlineStr">
@@ -5566,6 +8730,14 @@
           <t>357.0</t>
         </is>
       </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr"/>
+      <c r="F395" t="inlineStr"/>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="396">
       <c r="A396" t="inlineStr">
@@ -5579,6 +8751,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" t="inlineStr"/>
+      <c r="F396" t="inlineStr"/>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="397">
       <c r="A397" t="inlineStr">
@@ -5592,6 +8772,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" t="inlineStr"/>
+      <c r="F397" t="inlineStr"/>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="398">
       <c r="A398" t="inlineStr">
@@ -5605,6 +8793,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D398" t="inlineStr"/>
+      <c r="E398" t="inlineStr"/>
+      <c r="F398" t="inlineStr"/>
+      <c r="G398" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="399">
       <c r="A399" t="inlineStr">
@@ -5618,6 +8814,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D399" t="inlineStr"/>
+      <c r="E399" t="inlineStr"/>
+      <c r="F399" t="inlineStr"/>
+      <c r="G399" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="400">
       <c r="A400" t="inlineStr">
@@ -5631,6 +8835,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D400" t="inlineStr"/>
+      <c r="E400" t="inlineStr"/>
+      <c r="F400" t="inlineStr"/>
+      <c r="G400" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="401">
       <c r="A401" t="inlineStr">
@@ -5644,6 +8856,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D401" t="inlineStr"/>
+      <c r="E401" t="inlineStr"/>
+      <c r="F401" t="inlineStr"/>
+      <c r="G401" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="402">
       <c r="A402" t="inlineStr">
@@ -5657,6 +8877,14 @@
           <t>148.0</t>
         </is>
       </c>
+      <c r="D402" t="inlineStr"/>
+      <c r="E402" t="inlineStr"/>
+      <c r="F402" t="inlineStr"/>
+      <c r="G402" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="403">
       <c r="A403" t="inlineStr">
@@ -5670,6 +8898,14 @@
           <t>388.0</t>
         </is>
       </c>
+      <c r="D403" t="inlineStr"/>
+      <c r="E403" t="inlineStr"/>
+      <c r="F403" t="inlineStr"/>
+      <c r="G403" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
@@ -5683,6 +8919,14 @@
           <t>864.0</t>
         </is>
       </c>
+      <c r="D404" t="inlineStr"/>
+      <c r="E404" t="inlineStr"/>
+      <c r="F404" t="inlineStr"/>
+      <c r="G404" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="405">
       <c r="A405" t="inlineStr">
@@ -5696,6 +8940,14 @@
           <t>864.0</t>
         </is>
       </c>
+      <c r="D405" t="inlineStr"/>
+      <c r="E405" t="inlineStr"/>
+      <c r="F405" t="inlineStr"/>
+      <c r="G405" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="406">
       <c r="A406" t="inlineStr">
@@ -5709,6 +8961,14 @@
           <t>864.0</t>
         </is>
       </c>
+      <c r="D406" t="inlineStr"/>
+      <c r="E406" t="inlineStr"/>
+      <c r="F406" t="inlineStr"/>
+      <c r="G406" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="407">
       <c r="A407" t="inlineStr">
@@ -5722,6 +8982,14 @@
           <t>128.0</t>
         </is>
       </c>
+      <c r="D407" t="inlineStr"/>
+      <c r="E407" t="inlineStr"/>
+      <c r="F407" t="inlineStr"/>
+      <c r="G407" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="408">
       <c r="A408" t="inlineStr">
@@ -5735,6 +9003,14 @@
           <t>188.0</t>
         </is>
       </c>
+      <c r="D408" t="inlineStr"/>
+      <c r="E408" t="inlineStr"/>
+      <c r="F408" t="inlineStr"/>
+      <c r="G408" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="409">
       <c r="A409" t="inlineStr">
@@ -5748,6 +9024,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D409" t="inlineStr"/>
+      <c r="E409" t="inlineStr"/>
+      <c r="F409" t="inlineStr"/>
+      <c r="G409" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
@@ -5761,6 +9045,14 @@
           <t>129.0</t>
         </is>
       </c>
+      <c r="D410" t="inlineStr"/>
+      <c r="E410" t="inlineStr"/>
+      <c r="F410" t="inlineStr"/>
+      <c r="G410" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="411">
       <c r="A411" t="inlineStr">
@@ -5774,6 +9066,14 @@
           <t>158.0</t>
         </is>
       </c>
+      <c r="D411" t="inlineStr"/>
+      <c r="E411" t="inlineStr"/>
+      <c r="F411" t="inlineStr"/>
+      <c r="G411" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="412">
       <c r="A412" t="inlineStr">
@@ -5787,6 +9087,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D412" t="inlineStr"/>
+      <c r="E412" t="inlineStr"/>
+      <c r="F412" t="inlineStr"/>
+      <c r="G412" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="413">
       <c r="A413" t="inlineStr">
@@ -5800,6 +9108,14 @@
           <t>109.0</t>
         </is>
       </c>
+      <c r="D413" t="inlineStr"/>
+      <c r="E413" t="inlineStr"/>
+      <c r="F413" t="inlineStr"/>
+      <c r="G413" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="414">
       <c r="A414" t="inlineStr">
@@ -5813,6 +9129,14 @@
           <t>39.0</t>
         </is>
       </c>
+      <c r="D414" t="inlineStr"/>
+      <c r="E414" t="inlineStr"/>
+      <c r="F414" t="inlineStr"/>
+      <c r="G414" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="415">
       <c r="A415" t="inlineStr">
@@ -5826,6 +9150,14 @@
           <t>128.0</t>
         </is>
       </c>
+      <c r="D415" t="inlineStr"/>
+      <c r="E415" t="inlineStr"/>
+      <c r="F415" t="inlineStr"/>
+      <c r="G415" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="416">
       <c r="A416" t="inlineStr">
@@ -5839,6 +9171,14 @@
           <t>128.0</t>
         </is>
       </c>
+      <c r="D416" t="inlineStr"/>
+      <c r="E416" t="inlineStr"/>
+      <c r="F416" t="inlineStr"/>
+      <c r="G416" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="417">
       <c r="A417" t="inlineStr">
@@ -5852,6 +9192,14 @@
           <t>89.0</t>
         </is>
       </c>
+      <c r="D417" t="inlineStr"/>
+      <c r="E417" t="inlineStr"/>
+      <c r="F417" t="inlineStr"/>
+      <c r="G417" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="418">
       <c r="A418" t="inlineStr">
@@ -5865,6 +9213,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D418" t="inlineStr"/>
+      <c r="E418" t="inlineStr"/>
+      <c r="F418" t="inlineStr"/>
+      <c r="G418" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="419">
       <c r="A419" t="inlineStr">
@@ -5878,6 +9234,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D419" t="inlineStr"/>
+      <c r="E419" t="inlineStr"/>
+      <c r="F419" t="inlineStr"/>
+      <c r="G419" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -5891,6 +9255,14 @@
           <t>328.0</t>
         </is>
       </c>
+      <c r="D420" t="inlineStr"/>
+      <c r="E420" t="inlineStr"/>
+      <c r="F420" t="inlineStr"/>
+      <c r="G420" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="421">
       <c r="A421" t="inlineStr">
@@ -5904,6 +9276,14 @@
           <t>99.0</t>
         </is>
       </c>
+      <c r="D421" t="inlineStr"/>
+      <c r="E421" t="inlineStr"/>
+      <c r="F421" t="inlineStr"/>
+      <c r="G421" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="422">
       <c r="A422" t="inlineStr">
@@ -5917,6 +9297,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D422" t="inlineStr"/>
+      <c r="E422" t="inlineStr"/>
+      <c r="F422" t="inlineStr"/>
+      <c r="G422" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="423">
       <c r="A423" t="inlineStr">
@@ -5930,6 +9318,14 @@
           <t>59.0</t>
         </is>
       </c>
+      <c r="D423" t="inlineStr"/>
+      <c r="E423" t="inlineStr"/>
+      <c r="F423" t="inlineStr"/>
+      <c r="G423" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="424">
       <c r="A424" t="inlineStr">
@@ -5943,6 +9339,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D424" t="inlineStr"/>
+      <c r="E424" t="inlineStr"/>
+      <c r="F424" t="inlineStr"/>
+      <c r="G424" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
@@ -5956,6 +9360,14 @@
           <t>79.0</t>
         </is>
       </c>
+      <c r="D425" t="inlineStr"/>
+      <c r="E425" t="inlineStr"/>
+      <c r="F425" t="inlineStr"/>
+      <c r="G425" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
@@ -5969,6 +9381,14 @@
           <t>88.0</t>
         </is>
       </c>
+      <c r="D426" t="inlineStr"/>
+      <c r="E426" t="inlineStr"/>
+      <c r="F426" t="inlineStr"/>
+      <c r="G426" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -5982,6 +9402,14 @@
           <t>69.0</t>
         </is>
       </c>
+      <c r="D427" t="inlineStr"/>
+      <c r="E427" t="inlineStr"/>
+      <c r="F427" t="inlineStr"/>
+      <c r="G427" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="428">
       <c r="A428" t="inlineStr">
@@ -5995,6 +9423,14 @@
           <t>49.0</t>
         </is>
       </c>
+      <c r="D428" t="inlineStr"/>
+      <c r="E428" t="inlineStr"/>
+      <c r="F428" t="inlineStr"/>
+      <c r="G428" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="429">
       <c r="A429" t="inlineStr">
@@ -6008,6 +9444,14 @@
           <t>118.0</t>
         </is>
       </c>
+      <c r="D429" t="inlineStr"/>
+      <c r="E429" t="inlineStr"/>
+      <c r="F429" t="inlineStr"/>
+      <c r="G429" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="430">
       <c r="A430" t="inlineStr">
@@ -6021,6 +9465,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D430" t="inlineStr"/>
+      <c r="E430" t="inlineStr"/>
+      <c r="F430" t="inlineStr"/>
+      <c r="G430" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="431">
       <c r="A431" t="inlineStr">
@@ -6034,6 +9486,14 @@
           <t>8.0</t>
         </is>
       </c>
+      <c r="D431" t="inlineStr"/>
+      <c r="E431" t="inlineStr"/>
+      <c r="F431" t="inlineStr"/>
+      <c r="G431" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="432">
       <c r="A432" t="inlineStr">
@@ -6047,6 +9507,14 @@
           <t>6.0</t>
         </is>
       </c>
+      <c r="D432" t="inlineStr"/>
+      <c r="E432" t="inlineStr"/>
+      <c r="F432" t="inlineStr"/>
+      <c r="G432" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="433">
       <c r="A433" t="inlineStr">
@@ -6060,6 +9528,14 @@
           <t>78.0</t>
         </is>
       </c>
+      <c r="D433" t="inlineStr"/>
+      <c r="E433" t="inlineStr"/>
+      <c r="F433" t="inlineStr"/>
+      <c r="G433" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="434">
       <c r="A434" t="inlineStr">
@@ -6073,6 +9549,14 @@
           <t>108.0</t>
         </is>
       </c>
+      <c r="D434" t="inlineStr"/>
+      <c r="E434" t="inlineStr"/>
+      <c r="F434" t="inlineStr"/>
+      <c r="G434" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="435">
       <c r="A435" t="inlineStr">
@@ -6086,6 +9570,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D435" t="inlineStr"/>
+      <c r="E435" t="inlineStr"/>
+      <c r="F435" t="inlineStr"/>
+      <c r="G435" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="436">
       <c r="A436" t="inlineStr">
@@ -6099,6 +9591,14 @@
           <t>138.0</t>
         </is>
       </c>
+      <c r="D436" t="inlineStr"/>
+      <c r="E436" t="inlineStr"/>
+      <c r="F436" t="inlineStr"/>
+      <c r="G436" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="437">
       <c r="A437" t="inlineStr">
@@ -6112,6 +9612,14 @@
           <t>128.0</t>
         </is>
       </c>
+      <c r="D437" t="inlineStr"/>
+      <c r="E437" t="inlineStr"/>
+      <c r="F437" t="inlineStr"/>
+      <c r="G437" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="438">
       <c r="A438" t="inlineStr">
@@ -6125,6 +9633,14 @@
           <t>108.0</t>
         </is>
       </c>
+      <c r="D438" t="inlineStr"/>
+      <c r="E438" t="inlineStr"/>
+      <c r="F438" t="inlineStr"/>
+      <c r="G438" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="439">
       <c r="A439" t="inlineStr">
@@ -6138,6 +9654,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D439" t="inlineStr"/>
+      <c r="E439" t="inlineStr"/>
+      <c r="F439" t="inlineStr"/>
+      <c r="G439" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="440">
       <c r="A440" t="inlineStr">
@@ -6151,6 +9675,14 @@
           <t>108.0</t>
         </is>
       </c>
+      <c r="D440" t="inlineStr"/>
+      <c r="E440" t="inlineStr"/>
+      <c r="F440" t="inlineStr"/>
+      <c r="G440" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
@@ -6164,6 +9696,14 @@
           <t>198.0</t>
         </is>
       </c>
+      <c r="D441" t="inlineStr"/>
+      <c r="E441" t="inlineStr"/>
+      <c r="F441" t="inlineStr"/>
+      <c r="G441" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -6177,6 +9717,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D442" t="inlineStr"/>
+      <c r="E442" t="inlineStr"/>
+      <c r="F442" t="inlineStr"/>
+      <c r="G442" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
@@ -6190,6 +9738,14 @@
           <t>108.0</t>
         </is>
       </c>
+      <c r="D443" t="inlineStr"/>
+      <c r="E443" t="inlineStr"/>
+      <c r="F443" t="inlineStr"/>
+      <c r="G443" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
@@ -6203,6 +9759,14 @@
           <t>118.0</t>
         </is>
       </c>
+      <c r="D444" t="inlineStr"/>
+      <c r="E444" t="inlineStr"/>
+      <c r="F444" t="inlineStr"/>
+      <c r="G444" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" t="inlineStr">
@@ -6216,6 +9780,14 @@
           <t>168.0</t>
         </is>
       </c>
+      <c r="D445" t="inlineStr"/>
+      <c r="E445" t="inlineStr"/>
+      <c r="F445" t="inlineStr"/>
+      <c r="G445" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" t="inlineStr">
@@ -6229,6 +9801,14 @@
           <t>119.0</t>
         </is>
       </c>
+      <c r="D446" t="inlineStr"/>
+      <c r="E446" t="inlineStr"/>
+      <c r="F446" t="inlineStr"/>
+      <c r="G446" t="inlineStr">
+        <is>
+          <t>999</t>
+        </is>
+      </c>
     </row>
     <row r="447">
       <c r="A447" t="inlineStr">
@@ -6240,6 +9820,14 @@
       <c r="C447" t="inlineStr">
         <is>
           <t>168.0</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr"/>
+      <c r="E447" t="inlineStr"/>
+      <c r="F447" t="inlineStr"/>
+      <c r="G447" t="inlineStr">
+        <is>
+          <t>999</t>
         </is>
       </c>
     </row>
